--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487532_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487532_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6448</v>
+        <v>7.1474</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2796</v>
+        <v>7.2366</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3652</v>
+        <v>-0.0892</v>
       </c>
       <c r="G2" t="n">
         <v>8.2288</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8433</v>
+        <v>0.346</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1106</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7328</v>
+        <v>0.2783</v>
       </c>
       <c r="V2" t="n">
         <v>-0.4481</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3574</v>
+        <v>2.5575</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5709</v>
+        <v>4.8779</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2135</v>
+        <v>-2.3204</v>
       </c>
       <c r="G3" t="n">
         <v>4.2503</v>
@@ -688,13 +688,13 @@
         <v>0.9792</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4389</v>
+        <v>-0.2388</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1429</v>
+        <v>0.1641</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2959</v>
+        <v>-0.4029</v>
       </c>
       <c r="V3" t="n">
         <v>-2.4332</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2962</v>
+        <v>2.25</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4613</v>
+        <v>1.6825</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8349</v>
+        <v>0.5676</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8025</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5699</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2153</v>
+        <v>0.0059</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7852</v>
+        <v>0.5179</v>
       </c>
       <c r="V4" t="n">
         <v>1.5495</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4572</v>
+        <v>2.0596</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6698</v>
+        <v>2.1386</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2126</v>
+        <v>-0.0789</v>
       </c>
       <c r="G5" t="n">
         <v>0.1692</v>
@@ -844,13 +844,13 @@
         <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1036</v>
+        <v>-0.5012</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8316</v>
+        <v>-0.3629</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.272</v>
+        <v>-0.1384</v>
       </c>
       <c r="V5" t="n">
         <v>1.2166</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SOTO MARTINEZ</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1364</v>
+        <v>0.2748</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2.8924</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1364</v>
+        <v>-2.6176</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1364</v>
+        <v>0.883</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.4814</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1364</v>
+        <v>1.3645</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3.8851</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.3998</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.4853</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1364</v>
+        <v>-3.0021</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.8812</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1364</v>
+        <v>-2.1209</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1336</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.258</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.2923</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.0343</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1428</v>
+        <v>0.206</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5301</v>
+        <v>-0.3684</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3873</v>
+        <v>0.5744</v>
       </c>
       <c r="G7" t="n">
         <v>0.9316</v>
@@ -1000,13 +1000,13 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4869</v>
+        <v>-0.1381</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2023</v>
+        <v>-0.0406</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2846</v>
+        <v>-0.0975</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>A. SOTO MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4696</v>
+        <v>0.1364</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0143</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4839</v>
+        <v>0.1364</v>
       </c>
       <c r="G8" t="n">
-        <v>0.883</v>
+        <v>0.1364</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4814</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3645</v>
+        <v>0.1364</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8851</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3998</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4853</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.0021</v>
+        <v>0.1364</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8812</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1209</v>
+        <v>0.1364</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5668</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1336</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5668</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0025</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1704</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1679</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1164</v>
+        <v>-2.2349</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7877</v>
+        <v>-1.9329</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3287</v>
+        <v>-0.302</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9554</v>
@@ -1156,13 +1156,13 @@
         <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3678</v>
+        <v>0.2492</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0288</v>
+        <v>-0.1165</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3389</v>
+        <v>0.3657</v>
       </c>
       <c r="V9" t="n">
         <v>0.2754</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7889</v>
+        <v>-2.4101</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6026</v>
+        <v>-1.7049</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1864</v>
+        <v>-0.7052</v>
       </c>
       <c r="G10" t="n">
         <v>0.7012</v>
@@ -1234,13 +1234,13 @@
         <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7067</v>
+        <v>-0.3279</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0723</v>
+        <v>-0.1747</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6344</v>
+        <v>-0.1532</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0695</v>
+        <v>-4.8054</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6191</v>
+        <v>-1.8132</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4504</v>
+        <v>-2.9922</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.837</v>
+        <v>-2.0234</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2497</v>
+        <v>0.1794</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5873</v>
+        <v>-2.2028</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7537</v>
+        <v>-0.5558</v>
       </c>
       <c r="K11" t="n">
         <v>0.0408</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.7946</v>
+        <v>-0.5966</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0833</v>
+        <v>-1.4677</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2905</v>
+        <v>0.1385</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7927</v>
+        <v>-1.6062</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3917</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3758</v>
+        <v>-0.1529</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3098</v>
+        <v>-0.0823</v>
       </c>
       <c r="U11" t="n">
-        <v>0.06610000000000001</v>
+        <v>-0.0706</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2166</v>
+        <v>-2.4332</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2166</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6647</v>
+        <v>-4.9473</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5656</v>
+        <v>-2.5236</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0992</v>
+        <v>-2.4237</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0234</v>
+        <v>-3.837</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1794</v>
+        <v>-1.2497</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2028</v>
+        <v>-2.5873</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5558</v>
+        <v>-1.7537</v>
       </c>
       <c r="K12" t="n">
         <v>0.0408</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5966</v>
+        <v>-1.7946</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4677</v>
+        <v>-2.0833</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1385</v>
+        <v>-1.2905</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6062</v>
+        <v>-0.7927</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0122</v>
+        <v>0.498</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1653</v>
+        <v>0.4052</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1775</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4332</v>
+        <v>-1.2166</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4332</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3598999999999997</v>
+        <v>0.2339999999999991</v>
       </c>
       <c r="E13" t="n">
-        <v>9.8908</v>
+        <v>10.485</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.2509</v>
+        <v>-10.2508</v>
       </c>
       <c r="G13" t="n">
         <v>5.682199999999998</v>
@@ -1468,16 +1468,16 @@
         <v>10.7715</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5939999999999999</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0203</v>
+        <v>-0.4265</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4265</v>
+        <v>0.4264000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.4896</v>
+        <v>-3.489599999999999</v>
       </c>
       <c r="W13" t="n">
         <v>4.6937</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5274</v>
+        <v>3.586</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2485</v>
+        <v>4.3707</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2789</v>
+        <v>-0.7847</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3468</v>
+        <v>2.5812</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0637</v>
+        <v>0.3535</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4104</v>
+        <v>2.2276</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3385</v>
+        <v>4.3166</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3845</v>
+        <v>0.6243</v>
       </c>
       <c r="L14" t="n">
-        <v>3.723</v>
+        <v>3.6922</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0083</v>
+        <v>-1.7354</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6791</v>
+        <v>-0.2708</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6874</v>
+        <v>-1.4646</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1064</v>
+        <v>0.2267</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.09</v>
+        <v>0.0541</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1964</v>
+        <v>0.1726</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1217</v>
+        <v>-0.397</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1217</v>
+        <v>-0.397</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6705</v>
+        <v>3.3005</v>
       </c>
       <c r="E15" t="n">
-        <v>3.859</v>
+        <v>2.9415</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1885</v>
+        <v>0.3591</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5812</v>
+        <v>3.3468</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3535</v>
+        <v>-1.0637</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2276</v>
+        <v>4.4104</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3166</v>
+        <v>3.3385</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6243</v>
+        <v>-0.3845</v>
       </c>
       <c r="L15" t="n">
-        <v>3.6922</v>
+        <v>3.723</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7354</v>
+        <v>0.0083</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2708</v>
+        <v>-0.6791</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4646</v>
+        <v>0.6874</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6887</v>
+        <v>-0.1204</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4576</v>
+        <v>-0.397</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2311</v>
+        <v>0.2766</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.397</v>
+        <v>-0.1217</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.397</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.096</v>
+        <v>1.896</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5866</v>
+        <v>2.2384</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4906</v>
+        <v>-0.3424</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.8894</v>
+        <v>-1.4753</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0765</v>
+        <v>0.6727</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.9659</v>
+        <v>-2.1479</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4522</v>
+        <v>1.3914</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5493</v>
+        <v>1.5549</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.1635</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.3416</v>
+        <v>-2.8666</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4729</v>
+        <v>-0.8822</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.8687</v>
+        <v>-1.9844</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1958</v>
+        <v>-1.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5668</v>
+        <v>1.9585</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0863</v>
+        <v>-0.0566</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6805</v>
+        <v>-0.4111</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4059</v>
+        <v>0.3545</v>
       </c>
       <c r="V16" t="n">
-        <v>3.5281</v>
+        <v>2.6445</v>
       </c>
       <c r="W16" t="n">
-        <v>3.6498</v>
+        <v>2.4332</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1217</v>
+        <v>0.2113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1524</v>
+        <v>1.471</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4116</v>
+        <v>2.3371</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7408</v>
+        <v>-0.866</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9067</v>
+        <v>0.9483</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0483</v>
+        <v>1.589</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.6407</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1212</v>
+        <v>3.0661</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3589</v>
+        <v>1.4495</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4802</v>
+        <v>1.6166</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7855</v>
+        <v>-2.1177</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4073</v>
+        <v>0.1396</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3782</v>
+        <v>-2.2573</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3709</v>
+        <v>2.1543</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8633</v>
+        <v>0.1517</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7079</v>
+        <v>-0.4376</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1553</v>
+        <v>0.5893</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9344</v>
+        <v>1.3051</v>
       </c>
       <c r="E18" t="n">
-        <v>1.723</v>
+        <v>3.8703</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7886</v>
+        <v>-2.5652</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9483</v>
+        <v>-3.8894</v>
       </c>
       <c r="H18" t="n">
-        <v>1.589</v>
+        <v>0.0765</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6407</v>
+        <v>-3.9659</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0661</v>
+        <v>0.4522</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4495</v>
+        <v>0.5493</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6166</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1177</v>
+        <v>-4.3416</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1396</v>
+        <v>-0.4729</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2573</v>
+        <v>-3.8687</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1751</v>
+        <v>-0.1958</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1543</v>
+        <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3849</v>
+        <v>0.2954</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0516</v>
+        <v>-0.0359</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6667</v>
+        <v>0.3313</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6083</v>
+        <v>3.5281</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8837</v>
+        <v>3.6498</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.492</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8072</v>
+        <v>0.4582</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4197</v>
+        <v>-0.6117</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6125</v>
+        <v>1.07</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4753</v>
+        <v>-0.9067</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6727</v>
+        <v>-0.0483</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.1479</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3914</v>
+        <v>-0.1212</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5549</v>
+        <v>0.3589</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1635</v>
+        <v>-0.4802</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8666</v>
+        <v>-0.7855</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8822</v>
+        <v>-0.4073</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.9844</v>
+        <v>-0.3782</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1454</v>
+        <v>1.1691</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2298</v>
+        <v>0.6846</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0844</v>
+        <v>0.4845</v>
       </c>
       <c r="V19" t="n">
-        <v>2.6445</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0434</v>
+        <v>-1.6294</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3664</v>
+        <v>-1.4687</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.677</v>
+        <v>-0.1607</v>
       </c>
       <c r="G20" t="n">
         <v>2.1223</v>
@@ -2014,13 +2014,13 @@
         <v>1.9585</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1483</v>
+        <v>0.5623</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1347</v>
+        <v>0.0323</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0137</v>
+        <v>0.5299</v>
       </c>
       <c r="V20" t="n">
         <v>-0.397</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4945</v>
+        <v>-3.5645</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2848</v>
+        <v>-2.3871</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2097</v>
+        <v>-1.1774</v>
       </c>
       <c r="G21" t="n">
         <v>-4.5156</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2378</v>
+        <v>0.1678</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0288</v>
+        <v>-0.0735</v>
       </c>
       <c r="U21" t="n">
-        <v>0.209</v>
+        <v>0.2413</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2902</v>
+        <v>-4.4163</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3464</v>
+        <v>-1.0394</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.9438</v>
+        <v>-3.3769</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8938</v>
@@ -2170,13 +2170,13 @@
         <v>1.3709</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6291</v>
+        <v>0.2448</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1494</v>
+        <v>0.1576</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4797</v>
+        <v>0.0872</v>
       </c>
       <c r="V22" t="n">
         <v>-1.159</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3598000000000008</v>
+        <v>2.4066</v>
       </c>
       <c r="E23" t="n">
-        <v>10.2508</v>
+        <v>10.2511</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.891</v>
+        <v>-7.8442</v>
       </c>
       <c r="G23" t="n">
         <v>-5.6822</v>
@@ -2227,7 +2227,7 @@
         <v>6.0985</v>
       </c>
       <c r="L23" t="n">
-        <v>7.1672</v>
+        <v>7.167200000000002</v>
       </c>
       <c r="M23" t="n">
         <v>-18.9479</v>
@@ -2248,13 +2248,13 @@
         <v>12.73</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5940000000000001</v>
+        <v>2.6408</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4265000000000003</v>
+        <v>-0.4265000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0206</v>
+        <v>3.0672</v>
       </c>
       <c r="V23" t="n">
         <v>3.4896</v>
